--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-model-card.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-model-card.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$72</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2804" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2843" uniqueCount="578">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>The official AI Model Card. It mandates the inclusion of intended purpose, risk assessments, and performance metrics as per the EU AI Act and GDPR.</t>
+    <t>A DocumentReference profile representing technical documentation about an AI system, such as intended use, limitations, risk-related information, performance-related information, and model documentation.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -448,7 +448,7 @@
     <t>DocumentReference.extension</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t xml:space="preserve">Extension
@@ -521,6 +521,22 @@
   </si>
   <si>
     <t>GDPR and AI Act privacy parameters. Third country transfer flags and data retention policies at the model level.</t>
+  </si>
+  <si>
+    <t>DocumentReference.extension:clinicalValidationStatus</t>
+  </si>
+  <si>
+    <t>clinicalValidationStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/fhir/eu-ai-transparency/StructureDefinition/ai-clinical-validation-status}
+</t>
+  </si>
+  <si>
+    <t>AI Clinical Validation Status</t>
+  </si>
+  <si>
+    <t>Documents whether the AI system is clinically validated, not clinically validated, under validation, or only technically validated.</t>
   </si>
   <si>
     <t>DocumentReference.modifierExtension</t>
@@ -812,11 +828,11 @@
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|5.0.0)
+    <t xml:space="preserve">Reference(http://example.org/fhir/eu-ai-transparency/StructureDefinition/eu-ai-device)
 </t>
   </si>
   <si>
-    <t>Who/what is the subject of the document</t>
+    <t>Reference to the specific AI System Device (Traceability)</t>
   </si>
   <si>
     <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
@@ -2115,12 +2131,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ71"/>
+  <dimension ref="A1:AQ72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.8203125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.1015625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="43.8203125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.98828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="19.22265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3640,48 +3656,46 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="O13" t="s" s="2">
-        <v>167</v>
-      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>18</v>
       </c>
@@ -3729,7 +3743,7 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3753,7 +3767,7 @@
         <v>18</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>137</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>18</v>
@@ -3767,14 +3781,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3787,25 +3801,25 @@
         <v>18</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>18</v>
@@ -3854,7 +3868,7 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3866,36 +3880,36 @@
         <v>18</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>175</v>
+        <v>18</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>179</v>
+        <v>18</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>181</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3906,7 +3920,7 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>18</v>
@@ -3918,18 +3932,20 @@
         <v>93</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>18</v>
       </c>
@@ -3977,13 +3993,13 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>18</v>
@@ -3992,44 +4008,44 @@
         <v>104</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>18</v>
+        <v>183</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>18</v>
+        <v>185</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>18</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>190</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>18</v>
@@ -4038,21 +4054,21 @@
         <v>18</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" t="s" s="2">
-        <v>194</v>
-      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>18</v>
       </c>
@@ -4100,13 +4116,13 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>18</v>
@@ -4118,16 +4134,16 @@
         <v>18</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>18</v>
+        <v>193</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>196</v>
+        <v>18</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>18</v>
@@ -4136,46 +4152,46 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>18</v>
+        <v>195</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>112</v>
+        <v>196</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" s="2"/>
+      <c r="O17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="N17" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>18</v>
       </c>
@@ -4199,13 +4215,13 @@
         <v>18</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>116</v>
+        <v>18</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>201</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>202</v>
+        <v>18</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>18</v>
@@ -4223,13 +4239,13 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>18</v>
@@ -4238,33 +4254,33 @@
         <v>104</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>207</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4272,16 +4288,16 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>93</v>
@@ -4290,13 +4306,13 @@
         <v>112</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4325,10 +4341,10 @@
         <v>116</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>18</v>
@@ -4346,10 +4362,10 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>92</v>
@@ -4361,33 +4377,33 @@
         <v>104</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>18</v>
+        <v>208</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>214</v>
+        <v>18</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>18</v>
+        <v>211</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4398,7 +4414,7 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>18</v>
@@ -4410,15 +4426,17 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>112</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>18</v>
@@ -4443,13 +4461,13 @@
         <v>18</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>221</v>
+        <v>116</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>18</v>
@@ -4467,13 +4485,13 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>18</v>
@@ -4485,13 +4503,13 @@
         <v>18</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>18</v>
@@ -4500,15 +4518,15 @@
         <v>18</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>18</v>
+        <v>221</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4516,13 +4534,13 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>18</v>
@@ -4531,17 +4549,15 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>18</v>
@@ -4551,7 +4567,7 @@
         <v>18</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>229</v>
+        <v>18</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>18</v>
@@ -4566,13 +4582,13 @@
         <v>18</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>18</v>
@@ -4590,13 +4606,13 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>18</v>
@@ -4605,47 +4621,47 @@
         <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>233</v>
+        <v>18</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>235</v>
+        <v>18</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>236</v>
+        <v>18</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>237</v>
+        <v>18</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>238</v>
+        <v>18</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>239</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>241</v>
+        <v>18</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>18</v>
@@ -4654,16 +4670,16 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4674,7 +4690,7 @@
         <v>18</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>18</v>
+        <v>234</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>18</v>
@@ -4689,13 +4705,13 @@
         <v>18</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>18</v>
@@ -4713,13 +4729,13 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>18</v>
@@ -4728,44 +4744,44 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>18</v>
+        <v>238</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>18</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>18</v>
+        <v>246</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>18</v>
@@ -4777,15 +4793,17 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>18</v>
@@ -4810,13 +4828,13 @@
         <v>18</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>18</v>
+        <v>251</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>18</v>
+        <v>252</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>18</v>
@@ -4834,13 +4852,13 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>18</v>
@@ -4849,33 +4867,33 @@
         <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AP22" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AQ22" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AM22" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="23" hidden="true">
-      <c r="A23" t="s" s="2">
-        <v>263</v>
-      </c>
       <c r="B23" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4883,28 +4901,28 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4955,48 +4973,48 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>267</v>
+        <v>18</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>18</v>
+        <v>265</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>18</v>
+        <v>266</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>18</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5019,17 +5037,15 @@
         <v>18</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>18</v>
@@ -5054,13 +5070,13 @@
         <v>18</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>245</v>
+        <v>18</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>277</v>
+        <v>18</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>278</v>
+        <v>18</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>18</v>
@@ -5078,7 +5094,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5087,25 +5103,25 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>18</v>
+        <v>273</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>18</v>
+        <v>274</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>196</v>
+        <v>18</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>18</v>
@@ -5116,10 +5132,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5139,18 +5155,20 @@
         <v>18</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>18</v>
@@ -5175,13 +5193,13 @@
         <v>18</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>18</v>
@@ -5199,7 +5217,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5220,13 +5238,13 @@
         <v>18</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>18</v>
+        <v>284</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>18</v>
+        <v>201</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>18</v>
@@ -5237,10 +5255,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5251,7 +5269,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>18</v>
@@ -5260,16 +5278,16 @@
         <v>18</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>218</v>
+        <v>287</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5296,14 +5314,14 @@
         <v>18</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>18</v>
       </c>
@@ -5320,16 +5338,16 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>293</v>
+        <v>18</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>104</v>
@@ -5341,16 +5359,16 @@
         <v>18</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>296</v>
+        <v>18</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>297</v>
+        <v>18</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>18</v>
@@ -5358,10 +5376,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5384,20 +5402,16 @@
         <v>18</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>18</v>
       </c>
@@ -5421,13 +5435,13 @@
         <v>18</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>18</v>
@@ -5445,7 +5459,7 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5454,7 +5468,7 @@
         <v>92</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>104</v>
@@ -5466,16 +5480,16 @@
         <v>18</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>18</v>
@@ -5483,10 +5497,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5506,19 +5520,23 @@
         <v>18</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>308</v>
+        <v>223</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>18</v>
       </c>
@@ -5542,13 +5560,13 @@
         <v>18</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>18</v>
+        <v>308</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>18</v>
+        <v>309</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>18</v>
@@ -5566,7 +5584,7 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5575,7 +5593,7 @@
         <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>18</v>
+        <v>310</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>104</v>
@@ -5587,16 +5605,16 @@
         <v>18</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AN28" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>313</v>
-      </c>
       <c r="AP28" t="s" s="2">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>18</v>
@@ -5604,14 +5622,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>316</v>
+        <v>18</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5630,17 +5648,15 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>18</v>
@@ -5689,7 +5705,7 @@
         <v>18</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5704,22 +5720,22 @@
         <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>321</v>
+        <v>18</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>322</v>
+        <v>18</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>18</v>
+        <v>318</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>18</v>
+        <v>319</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>18</v>
@@ -5727,21 +5743,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>18</v>
+        <v>321</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>18</v>
@@ -5753,16 +5769,16 @@
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5812,13 +5828,13 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>18</v>
@@ -5827,33 +5843,33 @@
         <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>18</v>
+        <v>327</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>333</v>
+        <v>18</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>334</v>
+        <v>18</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>335</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5873,23 +5889,21 @@
         <v>18</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>18</v>
       </c>
@@ -5937,7 +5951,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5952,33 +5966,33 @@
         <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>18</v>
+        <v>340</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5989,7 +6003,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>18</v>
@@ -6001,16 +6015,20 @@
         <v>18</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>183</v>
+        <v>342</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>18</v>
       </c>
@@ -6058,37 +6076,37 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AG32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>18</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>18</v>
@@ -6096,21 +6114,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>18</v>
@@ -6122,17 +6140,15 @@
         <v>18</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M33" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>166</v>
-      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>18</v>
@@ -6181,19 +6197,19 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI33" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AG33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="AJ33" t="s" s="2">
-        <v>146</v>
+        <v>18</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>18</v>
@@ -6205,7 +6221,7 @@
         <v>18</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>18</v>
@@ -6219,14 +6235,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>357</v>
+        <v>168</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6239,10 +6255,10 @@
         <v>18</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>140</v>
@@ -6254,11 +6270,9 @@
         <v>359</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>18</v>
       </c>
@@ -6330,7 +6344,7 @@
         <v>18</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>137</v>
+        <v>356</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>18</v>
@@ -6351,36 +6365,38 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>18</v>
+        <v>362</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>218</v>
+        <v>140</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O35" t="s" s="2">
-        <v>364</v>
+        <v>172</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>18</v>
@@ -6405,43 +6421,43 @@
         <v>18</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>361</v>
-      </c>
       <c r="AG35" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>18</v>
@@ -6450,16 +6466,16 @@
         <v>18</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>367</v>
+        <v>18</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>368</v>
+        <v>137</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>369</v>
+        <v>18</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>18</v>
@@ -6467,10 +6483,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6478,7 +6494,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>92</v>
@@ -6493,17 +6509,17 @@
         <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>371</v>
+        <v>223</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>18</v>
@@ -6528,13 +6544,13 @@
         <v>18</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>18</v>
+        <v>235</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>18</v>
+        <v>370</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>18</v>
+        <v>371</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>18</v>
@@ -6552,10 +6568,10 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>92</v>
@@ -6573,16 +6589,16 @@
         <v>18</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>18</v>
@@ -6590,10 +6606,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6616,17 +6632,17 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>18</v>
@@ -6675,7 +6691,7 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6693,30 +6709,30 @@
         <v>18</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>383</v>
+        <v>18</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>387</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6739,18 +6755,18 @@
         <v>18</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>18</v>
       </c>
@@ -6798,7 +6814,7 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6813,33 +6829,33 @@
         <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>330</v>
+        <v>18</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>18</v>
+        <v>388</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>18</v>
+        <v>391</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>18</v>
+        <v>392</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6850,7 +6866,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>18</v>
@@ -6859,19 +6875,19 @@
         <v>18</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>337</v>
+        <v>394</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6921,13 +6937,13 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>18</v>
@@ -6936,19 +6952,19 @@
         <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>18</v>
+        <v>335</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AN39" t="s" s="2">
-        <v>400</v>
-      </c>
       <c r="AO39" t="s" s="2">
-        <v>401</v>
+        <v>18</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>18</v>
@@ -6959,10 +6975,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6973,7 +6989,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>18</v>
@@ -6982,18 +6998,20 @@
         <v>18</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>183</v>
+        <v>342</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>347</v>
+        <v>401</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>18</v>
@@ -7042,19 +7060,19 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>349</v>
+        <v>400</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>350</v>
+        <v>18</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>18</v>
@@ -7063,13 +7081,13 @@
         <v>18</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>18</v>
+        <v>404</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>351</v>
+        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>18</v>
+        <v>406</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>18</v>
@@ -7080,21 +7098,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>18</v>
@@ -7106,17 +7124,15 @@
         <v>18</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>166</v>
-      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>18</v>
@@ -7165,19 +7181,19 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI41" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AG41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="AJ41" t="s" s="2">
-        <v>146</v>
+        <v>18</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>18</v>
@@ -7189,7 +7205,7 @@
         <v>18</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>18</v>
@@ -7203,14 +7219,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>357</v>
+        <v>168</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7223,10 +7239,10 @@
         <v>18</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>140</v>
@@ -7238,11 +7254,9 @@
         <v>359</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>18</v>
       </c>
@@ -7314,7 +7328,7 @@
         <v>18</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>137</v>
+        <v>356</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>18</v>
@@ -7328,44 +7342,46 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>18</v>
+        <v>362</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>218</v>
+        <v>140</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>406</v>
+        <v>363</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>407</v>
+        <v>364</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>18</v>
       </c>
@@ -7389,13 +7405,13 @@
         <v>18</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>221</v>
+        <v>18</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>409</v>
+        <v>18</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>410</v>
+        <v>18</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>18</v>
@@ -7413,19 +7429,19 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>405</v>
+        <v>365</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>18</v>
@@ -7434,16 +7450,16 @@
         <v>18</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>411</v>
+        <v>18</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>412</v>
+        <v>137</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>413</v>
+        <v>18</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>414</v>
+        <v>18</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>18</v>
@@ -7451,10 +7467,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7477,15 +7493,17 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>416</v>
+        <v>223</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>18</v>
@@ -7510,13 +7528,13 @@
         <v>18</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>18</v>
+        <v>226</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>18</v>
+        <v>414</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>18</v>
+        <v>415</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>18</v>
@@ -7534,7 +7552,7 @@
         <v>18</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>92</v>
@@ -7555,27 +7573,27 @@
         <v>18</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AQ44" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AO44" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>423</v>
-      </c>
       <c r="B45" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7589,7 +7607,7 @@
         <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>18</v>
@@ -7598,20 +7616,16 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>18</v>
       </c>
@@ -7659,10 +7673,10 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>92</v>
@@ -7680,27 +7694,27 @@
         <v>18</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>18</v>
+        <v>424</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>18</v>
+        <v>427</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>431</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7708,13 +7722,13 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>18</v>
@@ -7723,19 +7737,19 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>218</v>
+        <v>429</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="O46" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>18</v>
@@ -7760,13 +7774,13 @@
         <v>18</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>245</v>
+        <v>18</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>437</v>
+        <v>18</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>438</v>
+        <v>18</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>18</v>
@@ -7784,13 +7798,13 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>18</v>
@@ -7805,27 +7819,27 @@
         <v>18</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>439</v>
+        <v>18</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>442</v>
+        <v>18</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>443</v>
+        <v>436</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7833,13 +7847,13 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>18</v>
@@ -7848,19 +7862,19 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>337</v>
+        <v>223</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>18</v>
@@ -7885,13 +7899,13 @@
         <v>18</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>18</v>
+        <v>442</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>18</v>
+        <v>443</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>18</v>
@@ -7909,10 +7923,10 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>79</v>
@@ -7930,27 +7944,27 @@
         <v>18</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AN47" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="48" hidden="true">
-      <c r="A48" t="s" s="2">
-        <v>451</v>
-      </c>
       <c r="B48" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7958,31 +7972,35 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>183</v>
+        <v>342</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>347</v>
+        <v>450</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>451</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>18</v>
       </c>
@@ -8030,19 +8048,19 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>349</v>
+        <v>449</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>350</v>
+        <v>18</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>18</v>
@@ -8051,10 +8069,10 @@
         <v>18</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>18</v>
+        <v>454</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>351</v>
+        <v>455</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>18</v>
@@ -8068,21 +8086,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>18</v>
@@ -8094,17 +8112,15 @@
         <v>18</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>166</v>
-      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>18</v>
@@ -8153,19 +8169,19 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI49" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AG49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="AJ49" t="s" s="2">
-        <v>146</v>
+        <v>18</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>18</v>
@@ -8177,7 +8193,7 @@
         <v>18</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>18</v>
@@ -8191,14 +8207,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>357</v>
+        <v>168</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8211,10 +8227,10 @@
         <v>18</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>140</v>
@@ -8226,11 +8242,9 @@
         <v>359</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>18</v>
       </c>
@@ -8302,7 +8316,7 @@
         <v>18</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>137</v>
+        <v>356</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>18</v>
@@ -8314,44 +8328,48 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>18</v>
+        <v>362</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I51" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>18</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>455</v>
+        <v>140</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>456</v>
+        <v>363</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
       </c>
@@ -8399,19 +8417,19 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>454</v>
+        <v>365</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>18</v>
@@ -8420,27 +8438,27 @@
         <v>18</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>458</v>
+        <v>18</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>450</v>
+        <v>137</v>
       </c>
       <c r="AO51" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AP51" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>462</v>
-      </c>
       <c r="B52" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8448,28 +8466,28 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>94</v>
+        <v>460</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>348</v>
+        <v>462</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8520,19 +8538,19 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>349</v>
+        <v>459</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>350</v>
+        <v>18</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>18</v>
@@ -8541,38 +8559,38 @@
         <v>18</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>18</v>
+        <v>463</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>351</v>
+        <v>455</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>18</v>
+        <v>464</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>18</v>
+        <v>465</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>18</v>
+        <v>466</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>18</v>
@@ -8584,17 +8602,15 @@
         <v>18</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>166</v>
-      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>18</v>
@@ -8631,31 +8647,31 @@
         <v>18</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>464</v>
+        <v>18</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI53" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AG53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="AJ53" t="s" s="2">
-        <v>146</v>
+        <v>18</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>18</v>
@@ -8667,7 +8683,7 @@
         <v>18</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>18</v>
@@ -8679,46 +8695,46 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>466</v>
+        <v>358</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>18</v>
       </c>
@@ -8730,84 +8746,84 @@
         <v>18</v>
       </c>
       <c r="T54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AC54" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="U54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="Y54" t="s" s="2">
+      <c r="AD54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="Z54" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AQ54" t="s" s="2">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>476</v>
-      </c>
       <c r="B55" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8815,13 +8831,13 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>18</v>
@@ -8833,14 +8849,14 @@
         <v>112</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>18</v>
@@ -8853,7 +8869,7 @@
         <v>18</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>18</v>
@@ -8868,10 +8884,10 @@
         <v>116</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>118</v>
+        <v>476</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>18</v>
@@ -8889,7 +8905,7 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8898,7 +8914,7 @@
         <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>18</v>
+        <v>478</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>104</v>
@@ -8913,7 +8929,7 @@
         <v>18</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>18</v>
@@ -8922,15 +8938,15 @@
         <v>18</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>18</v>
+        <v>480</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8944,28 +8960,26 @@
         <v>92</v>
       </c>
       <c r="H56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J56" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="K56" t="s" s="2">
-        <v>485</v>
+        <v>112</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>18</v>
@@ -8978,7 +8992,7 @@
         <v>18</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>18</v>
+        <v>485</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>18</v>
@@ -8990,13 +9004,13 @@
         <v>18</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>18</v>
+        <v>486</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>18</v>
@@ -9014,7 +9028,7 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9023,7 +9037,7 @@
         <v>92</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>473</v>
+        <v>18</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>104</v>
@@ -9038,7 +9052,7 @@
         <v>18</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>18</v>
@@ -9047,15 +9061,15 @@
         <v>18</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>492</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9075,22 +9089,22 @@
         <v>18</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O57" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>18</v>
@@ -9103,7 +9117,7 @@
         <v>18</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>499</v>
+        <v>18</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>18</v>
@@ -9139,7 +9153,7 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9148,7 +9162,7 @@
         <v>92</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>18</v>
+        <v>478</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>104</v>
@@ -9163,7 +9177,7 @@
         <v>18</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>18</v>
@@ -9172,15 +9186,15 @@
         <v>18</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9194,7 +9208,7 @@
         <v>92</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>18</v>
@@ -9203,19 +9217,19 @@
         <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>18</v>
@@ -9228,7 +9242,7 @@
         <v>18</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>18</v>
+        <v>504</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>18</v>
@@ -9264,7 +9278,7 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9288,7 +9302,7 @@
         <v>18</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>18</v>
@@ -9297,15 +9311,15 @@
         <v>18</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>18</v>
+        <v>507</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9328,19 +9342,19 @@
         <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>485</v>
+        <v>509</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>18</v>
@@ -9389,7 +9403,7 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9413,7 +9427,7 @@
         <v>18</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>18</v>
@@ -9425,12 +9439,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9438,13 +9452,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>18</v>
@@ -9453,19 +9467,19 @@
         <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>183</v>
+        <v>490</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>18</v>
@@ -9478,7 +9492,7 @@
         <v>18</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>523</v>
+        <v>18</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>18</v>
@@ -9514,7 +9528,7 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9538,7 +9552,7 @@
         <v>18</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>18</v>
@@ -9550,12 +9564,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9563,13 +9577,13 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>18</v>
@@ -9578,17 +9592,19 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>371</v>
+        <v>188</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="O61" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>18</v>
@@ -9601,7 +9617,7 @@
         <v>18</v>
       </c>
       <c r="T61" t="s" s="2">
-        <v>18</v>
+        <v>528</v>
       </c>
       <c r="U61" t="s" s="2">
         <v>18</v>
@@ -9637,7 +9653,7 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9661,7 +9677,7 @@
         <v>18</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>18</v>
@@ -9698,19 +9714,21 @@
         <v>18</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>18</v>
       </c>
@@ -9782,7 +9800,7 @@
         <v>18</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>18</v>
@@ -9796,10 +9814,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9822,7 +9840,7 @@
         <v>18</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>538</v>
@@ -9903,7 +9921,7 @@
         <v>18</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>18</v>
@@ -9917,10 +9935,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9943,17 +9961,15 @@
         <v>18</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N64" t="s" s="2">
         <v>544</v>
       </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>18</v>
@@ -10026,7 +10042,7 @@
         <v>18</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>18</v>
@@ -10066,16 +10082,16 @@
         <v>18</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10125,7 +10141,7 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10149,7 +10165,7 @@
         <v>18</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>18</v>
@@ -10163,10 +10179,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10189,7 +10205,7 @@
         <v>18</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>553</v>
@@ -10197,7 +10213,9 @@
       <c r="M66" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="N66" s="2"/>
+      <c r="N66" t="s" s="2">
+        <v>555</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>18</v>
@@ -10246,7 +10264,7 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10270,7 +10288,7 @@
         <v>18</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>18</v>
+        <v>541</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>18</v>
@@ -10284,21 +10302,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>557</v>
+        <v>18</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>18</v>
@@ -10307,10 +10325,10 @@
         <v>18</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>337</v>
+        <v>537</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>558</v>
@@ -10318,9 +10336,7 @@
       <c r="M67" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="N67" t="s" s="2">
-        <v>560</v>
-      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>18</v>
@@ -10369,13 +10385,13 @@
         <v>18</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>18</v>
@@ -10390,16 +10406,16 @@
         <v>18</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>561</v>
+        <v>18</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>450</v>
+        <v>18</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>562</v>
+        <v>18</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>563</v>
+        <v>18</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>18</v>
@@ -10407,21 +10423,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>18</v>
+        <v>562</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>18</v>
@@ -10430,18 +10446,20 @@
         <v>18</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>183</v>
+        <v>342</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>347</v>
+        <v>563</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>565</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>18</v>
@@ -10490,19 +10508,19 @@
         <v>18</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>349</v>
+        <v>561</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>350</v>
+        <v>18</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>18</v>
@@ -10511,16 +10529,16 @@
         <v>18</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>18</v>
+        <v>566</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>351</v>
+        <v>455</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>18</v>
+        <v>567</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>18</v>
+        <v>568</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>18</v>
@@ -10528,21 +10546,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>18</v>
@@ -10554,17 +10572,15 @@
         <v>18</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M69" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>166</v>
-      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>18</v>
@@ -10613,19 +10629,19 @@
         <v>18</v>
       </c>
       <c r="AF69" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI69" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AG69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="AJ69" t="s" s="2">
-        <v>146</v>
+        <v>18</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>18</v>
@@ -10637,7 +10653,7 @@
         <v>18</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>18</v>
@@ -10651,14 +10667,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>357</v>
+        <v>168</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10671,10 +10687,10 @@
         <v>18</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>140</v>
@@ -10686,11 +10702,9 @@
         <v>359</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>18</v>
       </c>
@@ -10762,7 +10776,7 @@
         <v>18</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>137</v>
+        <v>356</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>18</v>
@@ -10776,42 +10790,46 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>18</v>
+        <v>362</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="J71" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>568</v>
+        <v>140</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>569</v>
+        <v>363</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>18</v>
       </c>
@@ -10835,68 +10853,189 @@
         <v>18</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>571</v>
+        <v>18</v>
       </c>
       <c r="Z71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="AA71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF71" t="s" s="2">
+      <c r="B72" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AO72" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="AG71" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
+      <c r="AP72" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ71">
+  <autoFilter ref="A1:AQ72">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10906,7 +11045,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI70">
+  <conditionalFormatting sqref="A2:AI71">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-model-card.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-model-card.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -485,10 +485,10 @@
 </t>
   </si>
   <si>
-    <t>Metrics &amp; Bias</t>
-  </si>
-  <si>
-    <t>Captures quantitative metrics and bias disclosures.</t>
+    <t>Performance metrics and bias information</t>
+  </si>
+  <si>
+    <t>Documents quantitative performance measures and optional disclosures concerning bias, subgroup performance, or limitations of the evaluation.</t>
   </si>
   <si>
     <t>DocumentReference.extension:training</t>
@@ -501,10 +501,10 @@
 </t>
   </si>
   <si>
-    <t>EHDS Permit &amp; Data Quality</t>
-  </si>
-  <si>
-    <t>Details regarding provenance, EHDS categories, and data quality.</t>
+    <t>Training data provenance and EHDS metadata</t>
+  </si>
+  <si>
+    <t>Documents the origin, relevant EHDS-related classifications, applicable permit identifiers, secondary-use purposes, and reported quality characteristics of data used to train or develop the AI system.</t>
   </si>
   <si>
     <t>DocumentReference.extension:privacy</t>
@@ -513,14 +513,14 @@
     <t>privacy</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/fhir/eu-ai-transparency/StructureDefinition/ai-privacy-metadata}
+    <t xml:space="preserve">Extension {http://example.org/fhir/eu-ai-transparency/StructureDefinition/ai-retention-information}
 </t>
   </si>
   <si>
-    <t>Transfer &amp; Retention</t>
-  </si>
-  <si>
-    <t>GDPR and AI Act privacy parameters. Third country transfer flags and data retention policies at the model level.</t>
+    <t>Privacy and retention metadata</t>
+  </si>
+  <si>
+    <t>Documents the stated retention duration for AI-related data, outputs, logs, or documentation.</t>
   </si>
   <si>
     <t>DocumentReference.extension:clinicalValidationStatus</t>
@@ -533,10 +533,10 @@
 </t>
   </si>
   <si>
-    <t>AI Clinical Validation Status</t>
-  </si>
-  <si>
-    <t>Documents whether the AI system is clinically validated, not clinically validated, under validation, or only technically validated.</t>
+    <t>Clinical validation status</t>
+  </si>
+  <si>
+    <t>Records the documented validation status of the AI system, such as clinically validated, under clinical validation, technically validated only, or not clinically validated.</t>
   </si>
   <si>
     <t>DocumentReference.modifierExtension</t>
@@ -653,7 +653,7 @@
     <t>DocumentReference.status</t>
   </si>
   <si>
-    <t>current | superseded | entered-in-error</t>
+    <t>Publication status of the model card</t>
   </si>
   <si>
     <t>The status of this document reference.</t>
@@ -739,7 +739,7 @@
     <t>DocumentReference.type</t>
   </si>
   <si>
-    <t>AI Model Card</t>
+    <t>AI Model Card document type</t>
   </si>
   <si>
     <t>Specifies the particular kind of document referenced  (e.g. History and Physical, Discharge Summary, Progress Note). This usually equates to the purpose of making the document referenced.</t>
@@ -750,7 +750,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/EUAIActCodeSystem"/&gt;
+    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/eu-ai-artifact-type-cs"/&gt;
     &lt;code value="model-card"/&gt;
     &lt;display value="AI Model Card"/&gt;
   &lt;/coding&gt;
@@ -832,7 +832,7 @@
 </t>
   </si>
   <si>
-    <t>Reference to the specific AI System Device (Traceability)</t>
+    <t>AI system described by this model card</t>
   </si>
   <si>
     <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
@@ -1037,7 +1037,7 @@
 </t>
   </si>
   <si>
-    <t>When this document reference was created</t>
+    <t>Date of model card publication</t>
   </si>
   <si>
     <t>When the document reference was created.</t>
@@ -1368,10 +1368,10 @@
 </t>
   </si>
   <si>
-    <t>Mandatory high-level clinical summary and limitations of the AI model.</t>
-  </si>
-  <si>
-    <t>Human-readable description of the source document.</t>
+    <t>Summary of the AI model card</t>
+  </si>
+  <si>
+    <t>High-level summary of the intended purpose, principal limitations, risks, performance, and operational considerations documented by the model card.</t>
   </si>
   <si>
     <t>What the document is about,  a terse summary of the document.</t>
@@ -1463,10 +1463,10 @@
 </t>
   </si>
   <si>
-    <t>Detailed technical documentation and risk assessments (PDF, HTML, etc.)</t>
-  </si>
-  <si>
-    <t>The document or URL of the document along with critical metadata to prove content has integrity.</t>
+    <t>Technical documentation and instructions for use</t>
+  </si>
+  <si>
+    <t>Technical documentation or instructions for use containing intended purpose, limitations, risk information, required maintenance and support measures, maintenance frequency, and required software updates.</t>
   </si>
   <si>
     <t>Composition.language, 
@@ -4275,7 +4275,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>202</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>92</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>93</v>
@@ -5741,7 +5741,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>320</v>
       </c>
@@ -5754,13 +5754,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>18</v>
@@ -9064,7 +9064,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>489</v>
       </c>
@@ -9080,10 +9080,10 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>18</v>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>92</v>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-model-card.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-model-card.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-model-card.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-model-card.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-model-card.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-model-card.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
